--- a/experiments/results/resnet_imagenet50/ImageNet-1K/ReAct/adaptive/std/results.xlsx
+++ b/experiments/results/resnet_imagenet50/ImageNet-1K/ReAct/adaptive/std/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -540,6 +540,154 @@
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>p=None,ash_p=None,rt=1.0,st=0.15,t=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>97.84999999999999</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.1,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.12,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>95.86</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.14,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.15,type=std</t>
         </is>
       </c>
     </row>
